--- a/03_BOM/DuAn_HMI_F7_V3.xlsx
+++ b/03_BOM/DuAn_HMI_F7_V3.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="171">
   <si>
     <t>Line #</t>
   </si>
@@ -608,12 +608,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -627,6 +621,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -675,22 +675,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -705,9 +693,21 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -992,7 +992,7 @@
   <dimension ref="A1:J36"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="21" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" style="15" customWidth="1"/>
     <col min="2" max="2" width="18.53125" customWidth="1"/>
     <col min="3" max="3" width="32.796875" customWidth="1"/>
     <col min="4" max="5" width="18.53125" customWidth="1"/>
@@ -1003,100 +1003,100 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-    </row>
-    <row r="2" spans="1:10" s="15" customFormat="1">
-      <c r="A2" s="22" t="s">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+    </row>
+    <row r="2" spans="1:10" s="9" customFormat="1">
+      <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="14" t="s">
+      <c r="B2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="8" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="11" customFormat="1">
-      <c r="A3" s="20">
-        <v>1</v>
-      </c>
-      <c r="B3" s="8" t="s">
+    <row r="3" spans="1:10" s="7" customFormat="1">
+      <c r="A3" s="14">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="H3" s="10">
-        <v>1</v>
-      </c>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-    </row>
-    <row r="4" spans="1:10" s="11" customFormat="1">
-      <c r="A4" s="20">
+      <c r="H3" s="6">
+        <v>1</v>
+      </c>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1">
+      <c r="A4" s="14">
         <f>A3+1</f>
         <v>2</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10">
-        <v>1</v>
-      </c>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6">
+        <v>1</v>
+      </c>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="20">
+      <c r="A5" s="14">
         <f t="shared" ref="A5:A36" si="0">A4+1</f>
         <v>3</v>
       </c>
@@ -1125,7 +1125,7 @@
       <c r="J5" s="1"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="20">
+      <c r="A6" s="14">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1154,7 +1154,7 @@
       <c r="J6" s="1"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="20">
+      <c r="A7" s="14">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -1182,39 +1182,39 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:10" s="7" customFormat="1">
-      <c r="A8" s="20">
+    <row r="8" spans="1:10" s="22" customFormat="1">
+      <c r="A8" s="19">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="21">
         <v>2</v>
       </c>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6" t="s">
+      <c r="I8" s="21"/>
+      <c r="J8" s="21" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="20">
+      <c r="A9" s="14">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -1243,7 +1243,7 @@
       <c r="J9" s="1"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="20">
+      <c r="A10" s="14">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -1272,7 +1272,7 @@
       <c r="J10" s="1"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="20">
+      <c r="A11" s="14">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -1301,7 +1301,7 @@
       <c r="J11" s="1"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="20">
+      <c r="A12" s="14">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -1329,87 +1329,87 @@
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:10" s="11" customFormat="1">
-      <c r="A13" s="20">
+    <row r="13" spans="1:10" s="7" customFormat="1">
+      <c r="A13" s="14">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F13" s="8"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10">
-        <v>1</v>
-      </c>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-    </row>
-    <row r="14" spans="1:10" s="11" customFormat="1">
-      <c r="A14" s="20">
+      <c r="F13" s="4"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6">
+        <v>1</v>
+      </c>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+    </row>
+    <row r="14" spans="1:10" s="7" customFormat="1">
+      <c r="A14" s="14">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F14" s="8"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10">
-        <v>1</v>
-      </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-    </row>
-    <row r="15" spans="1:10" s="11" customFormat="1">
-      <c r="A15" s="20">
+      <c r="F14" s="4"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6">
+        <v>1</v>
+      </c>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+    </row>
+    <row r="15" spans="1:10" s="7" customFormat="1">
+      <c r="A15" s="14">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="H15" s="10">
-        <v>1</v>
-      </c>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
+      <c r="H15" s="6">
+        <v>1</v>
+      </c>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="20">
+      <c r="A16" s="14">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
@@ -1438,7 +1438,7 @@
       <c r="J16" s="1"/>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="20">
+      <c r="A17" s="14">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -1467,7 +1467,7 @@
       <c r="J17" s="1"/>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="20">
+      <c r="A18" s="14">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -1496,7 +1496,7 @@
       <c r="J18" s="1"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="20">
+      <c r="A19" s="14">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
@@ -1525,7 +1525,7 @@
       <c r="J19" s="1"/>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="20">
+      <c r="A20" s="14">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
@@ -1554,7 +1554,7 @@
       <c r="J20" s="1"/>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="20">
+      <c r="A21" s="14">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
@@ -1583,7 +1583,7 @@
       <c r="J21" s="1"/>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="20">
+      <c r="A22" s="14">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -1612,7 +1612,7 @@
       <c r="J22" s="1"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="20">
+      <c r="A23" s="14">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
@@ -1641,7 +1641,7 @@
       <c r="J23" s="1"/>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="20">
+      <c r="A24" s="14">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
@@ -1670,7 +1670,7 @@
       <c r="J24" s="1"/>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="20">
+      <c r="A25" s="14">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
@@ -1699,7 +1699,7 @@
       <c r="J25" s="1"/>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="20">
+      <c r="A26" s="14">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
@@ -1727,58 +1727,58 @@
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
     </row>
-    <row r="27" spans="1:10" s="11" customFormat="1">
-      <c r="A27" s="20">
+    <row r="27" spans="1:10" s="7" customFormat="1">
+      <c r="A27" s="14">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10">
-        <v>1</v>
-      </c>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-    </row>
-    <row r="28" spans="1:10" s="11" customFormat="1">
-      <c r="A28" s="20">
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6">
+        <v>1</v>
+      </c>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+    </row>
+    <row r="28" spans="1:10" s="7" customFormat="1">
+      <c r="A28" s="14">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="E28" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10">
-        <v>1</v>
-      </c>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6">
+        <v>1</v>
+      </c>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="20">
+      <c r="A29" s="14">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
@@ -1794,7 +1794,7 @@
       <c r="E29" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="F29" s="9" t="s">
+      <c r="F29" s="5" t="s">
         <v>158</v>
       </c>
       <c r="G29" s="2" t="s">
@@ -1807,7 +1807,7 @@
       <c r="J29" s="1"/>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="20">
+      <c r="A30" s="14">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
@@ -1836,7 +1836,7 @@
       <c r="J30" s="1"/>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="20">
+      <c r="A31" s="14">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
@@ -1852,7 +1852,7 @@
       <c r="E31" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="F31" s="9" t="s">
+      <c r="F31" s="5" t="s">
         <v>158</v>
       </c>
       <c r="G31" s="2" t="s">
@@ -1865,7 +1865,7 @@
       <c r="J31" s="1"/>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="20">
+      <c r="A32" s="14">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
@@ -1893,37 +1893,39 @@
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
     </row>
-    <row r="33" spans="1:10">
-      <c r="A33" s="20">
+    <row r="33" spans="1:10" s="22" customFormat="1">
+      <c r="A33" s="19">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="G33" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="H33" s="1">
-        <v>1</v>
-      </c>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
+      <c r="H33" s="21">
+        <v>1</v>
+      </c>
+      <c r="I33" s="21"/>
+      <c r="J33" s="21" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="20">
+      <c r="A34" s="14">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
@@ -1952,7 +1954,7 @@
       <c r="J34" s="1"/>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="20">
+      <c r="A35" s="14">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
@@ -1981,25 +1983,25 @@
       <c r="J35" s="1"/>
     </row>
     <row r="36" spans="1:10" ht="54">
-      <c r="A36" s="20">
+      <c r="A36" s="14">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B36" s="16" t="s">
+      <c r="B36" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="18" t="s">
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="G36" s="19" t="s">
+      <c r="G36" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="H36" s="17"/>
-      <c r="I36" s="17"/>
-      <c r="J36" s="17" t="s">
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11" t="s">
         <v>170</v>
       </c>
     </row>
